--- a/excel/Blending-Base.xlsx
+++ b/excel/Blending-Base.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Model" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Super (x)</t>
   </si>
@@ -31,13 +31,22 @@
     <t xml:space="preserve">kg</t>
   </si>
   <si>
-    <t xml:space="preserve">Gesamtgewinn (EUR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gewinn: EUR/kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einschränkungen</t>
+    <t xml:space="preserve">Total profit (EUR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit: EUR/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constraints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arabica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robusta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand</t>
   </si>
 </sst>
 </file>
@@ -52,6 +61,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -111,8 +121,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -239,47 +253,62 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:D6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.14"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <f aca="false">$B$2*B3+$C$2*C3</f>
         <v>0</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>40</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <f aca="false">$B$3*B4+$C$3*C4</f>
-        <v>0</v>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
